--- a/data/Plant_Production_Headcount_MonthlyGallons.xlsx
+++ b/data/Plant_Production_Headcount_MonthlyGallons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviaarkema/Documents/Strategic Planning/CD_StrategicPlanning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4F3D44BB-400A-374C-91D8-ACD769A0C61B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8A09D1-7D1C-694D-9F95-A98E9BCAE820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{3BEBC5DF-F756-B545-AB3C-432FF6CAA199}"/>
   </bookViews>
@@ -433,7 +433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15CE29A4-9CCE-AF40-A71A-8E7ED57FF119}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -833,46 +833,6 @@
         <v>105960.5</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A26">
-        <v>88112.8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A27">
-        <v>100855.62</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A28">
-        <v>102402.06</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A29">
-        <v>92514.76</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A30">
-        <v>91447.94</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A31">
-        <v>87368.48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A32">
-        <v>93761.17</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A33">
-        <v>1096096.44</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/Plant_Production_Headcount_MonthlyGallons.xlsx
+++ b/data/Plant_Production_Headcount_MonthlyGallons.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/oliviaarkema/Documents/Strategic Planning/CD_StrategicPlanning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC8A09D1-7D1C-694D-9F95-A98E9BCAE820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB0D04F7-B853-6347-99D2-95963794FB75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1100" yWindow="820" windowWidth="28040" windowHeight="17440" xr2:uid="{3BEBC5DF-F756-B545-AB3C-432FF6CAA199}"/>
   </bookViews>
@@ -435,6 +435,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15CE29A4-9CCE-AF40-A71A-8E7ED57FF119}">
   <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="4" max="4" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
